--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 16:00 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 16:52 | 차트: 98개</t>
         </is>
       </c>
     </row>
@@ -577,22 +577,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>20건</t>
+          <t>10.0건</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>8건</t>
+          <t>4.00건</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>-12건</t>
+          <t>-6.0건</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -614,22 +614,22 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>이동완료 호출 건수</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>15건</t>
+          <t>7.50건</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>8건</t>
+          <t>4.00건</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>-7건</t>
+          <t>-3.5건</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>총 탑승객 수</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>19명</t>
+          <t>9.50명</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>14명</t>
+          <t>7.00명</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>-5명</t>
+          <t>-2.5명</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1058,32 +1058,32 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>신규 지역 회원</t>
+          <t>신규 지역 회원(일평균)</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>6명</t>
+          <t>3.00명</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>3명</t>
+          <t>3.00명</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>-3명</t>
+          <t>+0.0명</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>-50.0%</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>⚠ 감소</t>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>유지</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1126,7 +1126,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>▼ 실시간 호출 건수 (-60.0%)</t>
+          <t>▼ 실시간 호출 건수(일평균) (-60.0%)</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>가호출 수</t>
+          <t>가호출 수(일평균)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -1207,12 +1207,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>배차실패 건수</t>
+          <t>배차실패 건수(일평균)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1244,12 +1244,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>호출취소 건수</t>
+          <t>호출취소 건수(일평균)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -1318,7 +1318,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -1392,7 +1392,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>▼ 이동완료 호출 건수 (-46.7%)</t>
+          <t>▼ 이동완료 호출 건수(일평균) (-46.7%)</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>이동완료 호출 건수</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>미탑승 건수</t>
+          <t>미탑승 건수(일평균)</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -1510,12 +1510,12 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>이동완료 호출 건수</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>호출취소 건수</t>
+          <t>호출취소 건수(일평균)</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>이동완료 호출 건수</t>
+          <t>이동완료 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>배차실패 건수</t>
+          <t>배차실패 건수(일평균)</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>▼ 총 탑승객 수 (-26.3%)</t>
+          <t>▼ 총 탑승객 수(일평균) (-26.3%)</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>총 탑승객 수</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>동승 인원 분포</t>
+          <t>동승 인원 분포(일평균)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1665,7 +1665,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>총 탑승객 수</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>총 탑승객 수</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>총 탑승객 수</t>
+          <t>총 탑승객 수(일평균)</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>동승 인원 분포</t>
+          <t>동승 인원 분포(일평균)</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>동승 인원 분포</t>
+          <t>동승 인원 분포(일평균)</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>신규 지역 회원</t>
+          <t>신규 지역 회원(일평균)</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -2467,126 +2467,8 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>▼ 신규 지역 회원 (-50.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>세부지표</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>비교기간</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>분석기간</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>변동값</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>변동률</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>신규 지역 회원</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>누적 지역 회원</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>+5.00</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>+25.0%</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>전체 회원 기반 성장세</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>신규 지역 회원</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>가호출 순 회원</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>-12.5%</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>가입 후 미이용(잠재 이탈) 회원</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A44:G44"/>
@@ -2594,7 +2476,6 @@
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A52:G52"/>
     <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2607,7 +2488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2789,7 +2670,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>실시간 호출 건수</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -3099,7 +2980,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>배차실패 건수</t>
+          <t>배차실패 건수(일평균)</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -3372,7 +3253,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>가호출 성공/실패 회원</t>
+          <t>가호출 성공/실패 회원(일평균)</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -3593,9 +3474,128 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>─ 신규 지역 회원(일평균) (+0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>신규 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>누적 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>+5.00</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>+25.0%</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>전체 회원 기반 성장세</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>신규 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>가호출 순 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>-12.5%</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>가입 후 미이용(잠재 이탈) 회원</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A35:G35"/>
@@ -3613,7 +3613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -3629,35 +3629,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>• 수요 감소: 호출(-60%), 이동완료(-47%), 탑승객(-26%) 모두 하락 — 분석기간 운행 2일(03/16,03/17), 비교기간 2일</t>
+          <t>• 가호출 성공률 상승: 38.5% → 87.5%, 가호출 시도 일평균 7.50건</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>• 이동완료율 75.0% → 100.0% (+25.0%p): 호출 8건 중 8건 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>• 가호출 성공률 상승: 38.5% → 87.5%, 가호출 시도 일평균 7.50건</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>• 성장 지표 긍정적: DAU -12%, 신규회원 6→3명(-50%), 누적 25명</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>• 호당 평균 탑승객 1.8명: 동승 이용 활발</t>
+          <t>• 성장 지표 긍정적: DAU -12%, 누적 25명</t>
         </is>
       </c>
     </row>

--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 16:52 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 16:53 | 차트: 98개</t>
         </is>
       </c>
     </row>

--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 16:55 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 16:56 | 차트: 98개</t>
         </is>
       </c>
     </row>
@@ -1830,22 +1830,22 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -2638,22 +2638,22 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+0.22</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7.9%</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -3369,22 +3369,22 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+49.0%p</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+127.0%</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">

--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1차 핵심지표" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 세부지표_변동" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 세부지표_안정" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="핵심 해석" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="핵심 해석" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부록_2차 세부지표_안정" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 16:56 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:15 | 차트: 98개</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>4.00건</t>
+          <t>4.0건</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -619,12 +619,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>7.50건</t>
+          <t>7.5건</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>4.00건</t>
+          <t>4.0건</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>9.50명</t>
+          <t>9.5명</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>7.00명</t>
+          <t>7.0명</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>9.50명</t>
+          <t>9.5명</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>7.00명</t>
+          <t>7.0명</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>2.76분</t>
+          <t>2.8분</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2.97분</t>
+          <t>3.0분</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>0.94배</t>
+          <t>0.9배</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1.07배</t>
+          <t>1.1배</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>1.00대</t>
+          <t>1.0대</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1.00대</t>
+          <t>1.0대</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>7.42시간</t>
+          <t>7.4시간</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>7.38시간</t>
+          <t>7.4시간</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>4.00명</t>
+          <t>4.0명</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>3.50명</t>
+          <t>3.5명</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>3.00명</t>
+          <t>3.0명</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>3.00명</t>
+          <t>3.0명</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1254,17 +1254,17 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1483,17 +1483,17 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1638,17 +1638,17 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1830,17 +1830,17 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1904,17 +1904,17 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1978,17 +1978,17 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>+0.17</t>
+          <t>+0.2</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2288,17 +2288,17 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2406,17 +2406,17 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2480,17 +2480,17 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>+0.49</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2517,17 +2517,17 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>+0.22</t>
+          <t>+0.2</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2562,6 +2562,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>3. 핵심 해석</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>• 수요 감소: 호출(-60%), 이동완료(-47%), 탑승객(-26%) 모두 하락 — 분석기간 운행 2일(03/16,03/17), 비교기간 2일</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>• 이동완료율 75.0% → 100.0% (+25.0%p): 호출 4건 중 4건 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>• 가호출 성공률 상승: 38.5% → 87.5%, 가호출 시도 일평균 7.5건</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>• 성장 지표 긍정적: DAU -12%, 누적 25명</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>• 호당 평균 탑승객 1.8명: 동승 이용 활발</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2577,7 +2639,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>3. 2차 세부지표_안정 (10% 이내 변동)</t>
+          <t>4. [부록] 2차 세부지표_안정 (10% 이내 변동)</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2700,17 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>+0.22</t>
+          <t>+0.2</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2712,7 +2774,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2722,7 +2784,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>+2.40</t>
+          <t>+2.4</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2786,17 +2848,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2828,12 +2890,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -2909,12 +2971,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -2941,7 +3003,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2951,7 +3013,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>+9.20</t>
+          <t>+9.2</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -2978,17 +3040,17 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>+0.13</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -3059,17 +3121,17 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -3096,17 +3158,17 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -3133,17 +3195,17 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -3214,17 +3276,17 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -3251,17 +3313,17 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -3288,17 +3350,17 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -3480,17 +3542,17 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -3517,17 +3579,17 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>+0.00</t>
+          <t>+0.0</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -3554,17 +3616,17 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -3635,17 +3697,17 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>+0.13</t>
+          <t>+0.1</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -3682,7 +3744,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>+0.17</t>
+          <t>+0.2</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -3763,7 +3825,7 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>+5.00</t>
+          <t>+5.0</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3790,17 +3852,17 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3827,45 +3889,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>4. 핵심 해석</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>• 가호출 성공률 상승: 38.5% → 87.5%, 가호출 시도 일평균 7.50건</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>• 성장 지표 긍정적: DAU -12%, 누적 25명</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:15 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:29 | 차트: 98개</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>가호출 대비 실호출 전환 저조</t>
+          <t>소폭 감소, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>배차 매칭 실패로 호출 유실</t>
+          <t>100% 감소, 주요 요인</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>이용자 자발적 취소 증가</t>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>차량 공급 부족에 따른 수요 억제</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>전화 호출 채널 비중 변화</t>
+          <t>비중 역방향 증가 (100%)</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>앱 호출 채널 비중 변화</t>
+          <t>비중 역방향 증가 (150%)</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>현장(직접) 호출 비중 변화</t>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>배차 후 미탑승(노쇼) 발생</t>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>이용자 자발적 취소</t>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>배차 매칭 실패</t>
+          <t>100% 감소, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>동승 비율 변화에 따른 탑승객 증감</t>
+          <t>동반 감소 (26%)</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>고령 이용자 호출 비중 변화</t>
+          <t>비중 큰 폭 감소, 주요 요인</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>성인 이용자 호출 비중 변화</t>
+          <t>비중 역방향 증가 (50%)</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>어린이/청소년 호출 비중 변화</t>
+          <t>신규 발생</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>평일 차량당 탑승객 변화</t>
+          <t>동반 감소 (26%)</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>주말 차량당 탑승객 변화</t>
+          <t>데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>동승 비율 변화에 따른 대당 탑승 변화</t>
+          <t>동반 감소 (26%)</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>수요 변동에 따른 대당 배분 변화</t>
+          <t>60% 감소, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>차량 수 변동에 따른 대당 배분 변화</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>극단적 우회 경로 발생</t>
+          <t>소폭 역방향 감소</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>우회 경로 증가가 이동시간 상승 유발</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>동승 증가로 경유지 추가</t>
+          <t>감소 전환 (26%)</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>일별 운행거리 편차</t>
+          <t>동반 감소 (28%)</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>수요 변동에 따른 운행거리 변화</t>
+          <t>60% 감소, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>차량 수 변동에 따른 대당 거리 변화</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>주간 활성도 추이 연동</t>
+          <t>분석기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>신규 유입 증감 영향</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>이용자 평균 연령 변화</t>
+          <t>증가 전환 (15%)</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>서비스 품질 불만에 따른 이탈</t>
+          <t>역방향 증가 (127%)</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>대기시간 증가에 따른 이탈</t>
+          <t>소폭 역방향 증가</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>평일 대기시간 변화</t>
+          <t>동반 증가 (8%)</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>주말 대기시간 변화</t>
+          <t>데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>극단적 장시간 대기 사례 발생</t>
+          <t>31% 증가, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>30분 이상 장시간 대기 비중</t>
+          <t>변동 없음</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>차량 공급 부족에 따른 대기 증가</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>수요 대비 공급 불균형</t>
+          <t>역방향 감소 (60%)</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대 이동시간 변화</t>
+          <t>감소 전환 (19%)</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>비피크 시간대 이동시간 변화</t>
+          <t>94% 증가, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>경로 우회에 따른 이동시간 증가</t>
+          <t>14% 증가, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>특정일 차량 미운행</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>기사 근무 미이행</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>차량 감소에 따른 배차 실패 연쇄</t>
+          <t>100% 감소</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>특정 차량 운행 시간 편차</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>공차 대기 시간 증가</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>수요 감소에 따른 공회전</t>
+          <t>동반 감소 (26%)</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>평일 가호출 성공률 변화</t>
+          <t>비중 큰 폭 증가, 주요 요인</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>주말 가호출 성공률 변화</t>
+          <t>데이터 없음</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대 가호출 성공률 변화</t>
+          <t>비중 큰 폭 증가, 주요 요인</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>가호출 실패 경험 이용자 증가</t>
+          <t>역방향 감소 (42%)</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>차량 공급 부족에 따른 매칭 실패</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>수요 급증 대비 공급 부족</t>
+          <t>감소 전환 (21%)</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>경로 이탈이 우회비율 증가 유발</t>
+          <t>14% 증가, 핵심 요인</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>경로 이탈이 이동시간 증가 유발</t>
+          <t>안정 유지, 영향 제한적</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>전체 회원 기반 성장세</t>
+          <t>25% 증가</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>가입 후 미이용(잠재 이탈) 회원</t>
+          <t>12% 감소</t>
         </is>
       </c>
     </row>

--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:29 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:30 | 차트: 98개</t>
         </is>
       </c>
     </row>

--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:33 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:43 | 차트: 98개</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>소폭 감소, 영향 제한적</t>
+          <t>가호출/실호출 동반 감소</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>100% 감소, 주요 요인</t>
+          <t>배차실패 건수 해소</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>변동 없음</t>
+          <t>발생 없음</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>1대 유지, 증차 여지 없음</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>비중 역방향 증가 (100%)</t>
+          <t>전화 25→50%</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>비중 역방향 증가 (150%)</t>
+          <t>앱 5→12%</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>드라이버 호출 비율</t>
+          <t>현장 호출 비율</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>비중 큰 폭 감소, 주요 요인</t>
+          <t>현장 70→38%</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>변동 없음</t>
+          <t>발생 없음</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>변동 없음</t>
+          <t>발생 없음</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>100% 감소, 핵심 요인</t>
+          <t>배차실패 건수 해소</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>비중 큰 폭 감소, 주요 요인</t>
+          <t>고령자(60+) 83→50%</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>비중 역방향 증가 (50%)</t>
+          <t>성인(20~50대) 17→25%</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>동반 감소 (26%)</t>
+          <t>평일 7.0명 (26% 감소)</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>1대 유지, 증차 여지 없음</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>소폭 역방향 감소</t>
+          <t>1.4배 안정</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>10.4분 안정</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>1대 유지, 증차 여지 없음</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>신규 3.0명/일 (0% 감소)</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>증가 전환 (15%)</t>
+          <t>평균 75세 (15% 증가)</t>
         </is>
       </c>
     </row>
@@ -2480,17 +2480,17 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+49.0%p</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>역방향 증가 (127%)</t>
+          <t>비중 역방향 증가 (127%)</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>소폭 역방향 증가</t>
+          <t>2.8→3.0분 증가</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>• 호당 평균 탑승객 1.8명: 동승 이용 활발</t>
+          <t>• 호출당 평균 탑승객 1.8명: 동승 이용 활발</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>동반 증가 (8%)</t>
+          <t>평일 3.0분 (8% 증가)</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>31% 증가, 핵심 요인</t>
+          <t>상위10% 10분, 장시간 대기</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>1대 유지, 증차 여지 없음</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>감소 전환 (19%)</t>
+          <t>11.5→9.3분 감소</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>94% 증가, 핵심 요인</t>
+          <t>9.8→19.0분 증가</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>14% 증가, 핵심 요인</t>
+          <t>0.9→1.1배 증가</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>0% 감소</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>1.0시간 유지</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>100% 감소</t>
+          <t>배차실패 건수 해소</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>9.3시간 유지</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>비중 큰 폭 증가, 주요 요인</t>
+          <t>평일 88% (127% 증가)</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>비중 큰 폭 증가, 주요 요인</t>
+          <t>피크 77% (50% 증가)</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>역방향 감소 (42%)</t>
+          <t>6.0→3.5명 감소</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>1대 유지, 증차 여지 없음</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>감소 전환 (21%)</t>
+          <t>가호출 21% 감소</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>14% 증가, 핵심 요인</t>
+          <t>0.9→1.1배 증가</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>안정 유지, 영향 제한적</t>
+          <t>10.4분 안정</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>25% 증가</t>
+          <t>누적 25명 (25% 증가)</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>12% 감소</t>
+          <t>4.0→3.5명 감소</t>
         </is>
       </c>
     </row>

--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-18 17:44 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 09:53 | 차트: 98개</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>⚠ 악화</t>
+          <t>⚠ 저하</t>
         </is>
       </c>
     </row>

--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:40 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:43 | 차트: 98개</t>
         </is>
       </c>
     </row>

--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:43 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:47 | 차트: 98개</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>⚠ 저하</t>
+          <t>저하</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>개선</t>
+          <t>⚠ 개선</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>⚠ 감소</t>
+          <t>감소</t>
         </is>
       </c>
     </row>

--- a/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
+++ b/shucle_report/동면/20260316_20260317/report_동면_20260316_20260317.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:52 | 차트: 98개</t>
+          <t>분석기간: 2026.03.16 ~ 03.17 | 비교기간: 2026.03.12 ~ 03.13 | 생성: 2026-03-19 13:53 | 차트: 98개</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
           <t>+7.9%</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>유지</t>
         </is>
@@ -822,7 +822,7 @@
           <t>+1.7%</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>유지</t>
         </is>
@@ -896,7 +896,7 @@
           <t>-0.4%</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>유지</t>
         </is>
@@ -1007,7 +1007,7 @@
           <t>+3.8%</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>유지</t>
         </is>
